--- a/source_data/SourceData_EDFig1.xlsx
+++ b/source_data/SourceData_EDFig1.xlsx
@@ -1074,7 +1074,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ThemeCat</t>
+          <t>TheMeCat</t>
         </is>
       </c>
       <c r="B4" t="n">

--- a/source_data/SourceData_EDFig1.xlsx
+++ b/source_data/SourceData_EDFig1.xlsx
@@ -618,13 +618,13 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E4" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F4" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -650,13 +650,13 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="F5" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -682,16 +682,16 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>93</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="F6" t="n">
-        <v>66</v>
+        <v>28</v>
       </c>
       <c r="G6" t="n">
-        <v>0.985</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
         <v>1</v>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E7" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F7" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G7" t="n">
         <v>0.992</v>
@@ -746,16 +746,16 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
-        <v>0.962</v>
+        <v>0.961</v>
       </c>
       <c r="H8" t="n">
         <v>0.977</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E9" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G9" t="n">
-        <v>0.96</v>
+        <v>0.922</v>
       </c>
       <c r="H9" t="n">
-        <v>0.976</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="10">
@@ -810,19 +810,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="E10" t="n">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="F10" t="n">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="G10" t="n">
-        <v>0.83</v>
+        <v>0.828</v>
       </c>
       <c r="H10" t="n">
-        <v>0.995</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="E11" t="n">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="F11" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="G11" t="n">
-        <v>0.372</v>
+        <v>0.359</v>
       </c>
       <c r="H11" t="n">
-        <v>0.791</v>
+        <v>0.773</v>
       </c>
     </row>
     <row r="12">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>289</v>
+        <v>232</v>
       </c>
       <c r="E12" t="n">
-        <v>175</v>
+        <v>133</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.166</v>
+        <v>0.113</v>
       </c>
       <c r="H12" t="n">
-        <v>0.406</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="13">
@@ -906,19 +906,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E13" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F13" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="G13" t="n">
-        <v>0.773</v>
+        <v>0.654</v>
       </c>
       <c r="H13" t="n">
-        <v>0.909</v>
+        <v>0.846</v>
       </c>
     </row>
     <row r="14">
@@ -938,19 +938,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="E14" t="n">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="F14" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.477</v>
+        <v>0.308</v>
       </c>
       <c r="H14" t="n">
-        <v>0.8179999999999999</v>
+        <v>0.6919999999999999</v>
       </c>
     </row>
     <row r="15">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>61</v>
+        <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.312</v>
+        <v>0.167</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5</v>
+        <v>0.278</v>
       </c>
     </row>
   </sheetData>
@@ -1081,13 +1081,13 @@
         <v>547</v>
       </c>
       <c r="C4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.962</v>
+        <v>0.965</v>
       </c>
       <c r="E4" t="n">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5">
@@ -1100,13 +1100,13 @@
         <v>194</v>
       </c>
       <c r="C5" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D5" t="n">
-        <v>0.99</v>
+        <v>0.985</v>
       </c>
       <c r="E5" t="n">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -1119,13 +1119,13 @@
         <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="D6" t="n">
-        <v>0.969</v>
+        <v>0.97</v>
       </c>
       <c r="E6" t="n">
-        <v>654</v>
+        <v>647</v>
       </c>
     </row>
   </sheetData>

--- a/source_data/SourceData_EDFig1.xlsx
+++ b/source_data/SourceData_EDFig1.xlsx
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E7" t="n">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F7" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G7" t="n">
         <v>0.992</v>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E8" t="n">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F8" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G8" t="n">
         <v>0.961</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E9" t="n">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F9" t="n">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G9" t="n">
-        <v>0.922</v>
+        <v>0.959</v>
       </c>
       <c r="H9" t="n">
-        <v>0.945</v>
+        <v>0.975</v>
       </c>
     </row>
     <row r="10">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E12" t="n">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.113</v>
+        <v>0.112</v>
       </c>
       <c r="H12" t="n">
-        <v>0.323</v>
+        <v>0.313</v>
       </c>
     </row>
     <row r="13">
@@ -973,16 +973,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.167</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>0.278</v>
+        <v>0.667</v>
       </c>
     </row>
   </sheetData>
@@ -1081,13 +1081,13 @@
         <v>547</v>
       </c>
       <c r="C4" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="D4" t="n">
-        <v>0.965</v>
+        <v>0.962</v>
       </c>
       <c r="E4" t="n">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="5">
@@ -1106,7 +1106,7 @@
         <v>0.985</v>
       </c>
       <c r="E5" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6">
@@ -1119,10 +1119,10 @@
         <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="D6" t="n">
-        <v>0.97</v>
+        <v>0.968</v>
       </c>
       <c r="E6" t="n">
         <v>647</v>

--- a/source_data/SourceData_EDFig1.xlsx
+++ b/source_data/SourceData_EDFig1.xlsx
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="D7" t="n">
+        <v>130</v>
+      </c>
+      <c r="E7" t="n">
+        <v>130</v>
+      </c>
+      <c r="F7" t="n">
         <v>129</v>
-      </c>
-      <c r="E7" t="n">
-        <v>129</v>
-      </c>
-      <c r="F7" t="n">
-        <v>128</v>
       </c>
       <c r="G7" t="n">
         <v>0.992</v>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E8" t="n">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F8" t="n">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G8" t="n">
         <v>0.961</v>
@@ -778,19 +778,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E9" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F9" t="n">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G9" t="n">
-        <v>0.959</v>
+        <v>0.922</v>
       </c>
       <c r="H9" t="n">
-        <v>0.975</v>
+        <v>0.945</v>
       </c>
     </row>
     <row r="10">
@@ -874,19 +874,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E12" t="n">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F12" t="n">
         <v>15</v>
       </c>
       <c r="G12" t="n">
-        <v>0.112</v>
+        <v>0.113</v>
       </c>
       <c r="H12" t="n">
-        <v>0.313</v>
+        <v>0.323</v>
       </c>
     </row>
     <row r="13">
@@ -973,16 +973,16 @@
         <v>32</v>
       </c>
       <c r="E15" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F15" t="n">
         <v>3</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5</v>
+        <v>0.167</v>
       </c>
       <c r="H15" t="n">
-        <v>0.667</v>
+        <v>0.278</v>
       </c>
     </row>
   </sheetData>
@@ -1081,13 +1081,13 @@
         <v>547</v>
       </c>
       <c r="C4" t="n">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="D4" t="n">
-        <v>0.962</v>
+        <v>0.965</v>
       </c>
       <c r="E4" t="n">
-        <v>492</v>
+        <v>494</v>
       </c>
     </row>
     <row r="5">
@@ -1106,7 +1106,7 @@
         <v>0.985</v>
       </c>
       <c r="E5" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="6">
@@ -1119,10 +1119,10 @@
         <v>741</v>
       </c>
       <c r="C6" t="n">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="D6" t="n">
-        <v>0.968</v>
+        <v>0.97</v>
       </c>
       <c r="E6" t="n">
         <v>647</v>
